--- a/data/trans_dic/Q17F_D_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 26,04</t>
+          <t>7,65; 28,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 26,13</t>
+          <t>6,91; 27,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 20,14</t>
+          <t>4,74; 20,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 17,55</t>
+          <t>3,44; 16,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 23,02</t>
+          <t>6,54; 25,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 13,09</t>
+          <t>3,16; 14,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 27,81</t>
+          <t>11,67; 27,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,55; 26,14</t>
+          <t>11,75; 25,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 21,53</t>
+          <t>8,77; 22,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 15,29</t>
+          <t>5,45; 15,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 21,41</t>
+          <t>10,41; 21,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 18,55</t>
+          <t>9,38; 19,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 29,08</t>
+          <t>10,95; 28,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 23,43</t>
+          <t>6,85; 23,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 19,93</t>
+          <t>6,8; 20,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 36,13</t>
+          <t>14,72; 36,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 27,84</t>
+          <t>13,79; 27,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 14,67</t>
+          <t>4,38; 14,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 18,84</t>
+          <t>8,88; 20,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 26,17</t>
+          <t>11,85; 25,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,51; 25,19</t>
+          <t>14,01; 24,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 15,72</t>
+          <t>6,65; 15,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 17,68</t>
+          <t>9,45; 18,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 27,87</t>
+          <t>15,14; 27,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 16,25</t>
+          <t>1,72; 14,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 22,96</t>
+          <t>6,93; 22,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,37</t>
+          <t>1,34; 11,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 17,82</t>
+          <t>3,37; 17,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 11,73</t>
+          <t>1,92; 11,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 12,23</t>
+          <t>3,59; 12,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 15,07</t>
+          <t>3,64; 13,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 19,24</t>
+          <t>7,01; 19,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,17</t>
+          <t>2,58; 10,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 13,85</t>
+          <t>6,2; 13,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,13</t>
+          <t>3,73; 10,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,57</t>
+          <t>6,37; 15,23</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 32,31</t>
+          <t>11,1; 32,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 23,63</t>
+          <t>7,28; 24,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 24,39</t>
+          <t>8,29; 25,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,96; 43,91</t>
+          <t>20,53; 45,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,49</t>
+          <t>0,87; 8,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 15,72</t>
+          <t>4,68; 15,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 24,77</t>
+          <t>10,26; 24,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 24,98</t>
+          <t>4,47; 25,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 13,01</t>
+          <t>4,67; 13,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 16,5</t>
+          <t>7,2; 16,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 21,6</t>
+          <t>11,36; 21,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 28,44</t>
+          <t>6,85; 28,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 23,76</t>
+          <t>4,03; 24,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 16,26</t>
+          <t>1,97; 16,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 30,38</t>
+          <t>2,99; 33,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,23; 44,38</t>
+          <t>11,78; 46,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 30,46</t>
+          <t>8,61; 30,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 23,34</t>
+          <t>8,67; 24,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 18,82</t>
+          <t>2,0; 18,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,56; 32,06</t>
+          <t>11,09; 31,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,69; 22,99</t>
+          <t>8,25; 22,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 17,85</t>
+          <t>7,05; 17,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 19,94</t>
+          <t>4,47; 18,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 32,15</t>
+          <t>13,49; 31,51</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,52</t>
+          <t>0,0; 15,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 22,02</t>
+          <t>6,68; 22,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,13</t>
+          <t>1,85; 11,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 18,42</t>
+          <t>4,62; 19,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,76; 15,89</t>
+          <t>2,77; 16,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 17,67</t>
+          <t>5,84; 18,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 14,26</t>
+          <t>3,83; 13,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 19,98</t>
+          <t>4,92; 19,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 11,92</t>
+          <t>3,17; 12,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 16,77</t>
+          <t>7,39; 16,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,16</t>
+          <t>3,77; 10,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,13; 16,38</t>
+          <t>6,34; 16,04</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,68; 19,36</t>
+          <t>8,75; 20,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,07; 22,18</t>
+          <t>9,6; 21,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 27,0</t>
+          <t>12,63; 27,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,5; 34,45</t>
+          <t>18,44; 34,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,67</t>
+          <t>6,91; 16,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,54; 20,75</t>
+          <t>10,72; 20,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,22; 23,37</t>
+          <t>11,42; 22,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,23; 32,06</t>
+          <t>20,53; 32,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 15,86</t>
+          <t>8,4; 15,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,77; 19,5</t>
+          <t>11,73; 19,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,72; 23,21</t>
+          <t>13,36; 22,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,86; 30,77</t>
+          <t>21,03; 30,7</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,83</t>
+          <t>5,68; 15,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 16,21</t>
+          <t>5,63; 16,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,17</t>
+          <t>4,22; 11,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,19; 20,45</t>
+          <t>9,1; 19,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,13; 14,34</t>
+          <t>6,26; 14,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 14,71</t>
+          <t>6,65; 14,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 15,4</t>
+          <t>6,59; 15,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,38; 26,4</t>
+          <t>15,96; 26,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,6; 13,25</t>
+          <t>7,03; 13,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,65</t>
+          <t>7,22; 13,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,38; 12,22</t>
+          <t>6,61; 12,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,77; 21,82</t>
+          <t>14,68; 21,98</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,89</t>
+          <t>9,76; 15,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,16</t>
+          <t>10,09; 15,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,39</t>
+          <t>8,56; 13,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,37</t>
+          <t>15,55; 21,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,79</t>
+          <t>8,64; 12,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,44</t>
+          <t>8,78; 12,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,69; 14,64</t>
+          <t>10,52; 14,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,3; 21,22</t>
+          <t>13,77; 21,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,76; 12,96</t>
+          <t>9,77; 12,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,12</t>
+          <t>9,8; 12,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,23; 13,43</t>
+          <t>10,43; 13,52</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,51; 20,45</t>
+          <t>15,62; 20,42</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3593; 12385</t>
+          <t>3637; 13680</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3464; 14875</t>
+          <t>3933; 15724</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2976; 13649</t>
+          <t>3210; 13832</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2743; 12044</t>
+          <t>2363; 11219</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3993; 14263</t>
+          <t>4055; 15651</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2045; 11866</t>
+          <t>2861; 12720</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10702; 26062</t>
+          <t>10936; 25711</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9233; 19234</t>
+          <t>8641; 18772</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9067; 23585</t>
+          <t>9605; 24338</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7941; 22563</t>
+          <t>8038; 23091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16262; 34570</t>
+          <t>16807; 34671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12964; 26381</t>
+          <t>13333; 27585</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9334; 25102</t>
+          <t>9455; 24774</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5854; 20759</t>
+          <t>6065; 21081</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6974; 20659</t>
+          <t>7048; 21404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10472; 27109</t>
+          <t>11042; 27249</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18803; 36818</t>
+          <t>18236; 35937</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5955; 19957</t>
+          <t>5960; 19403</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14984; 32972</t>
+          <t>15544; 35005</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10451; 22951</t>
+          <t>10387; 22748</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31721; 55051</t>
+          <t>30617; 54068</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15090; 35321</t>
+          <t>14932; 35146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26207; 49253</t>
+          <t>26320; 50282</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24766; 45344</t>
+          <t>24634; 45113</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>915; 8862</t>
+          <t>936; 7939</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5174; 19603</t>
+          <t>5921; 19442</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>845; 7843</t>
+          <t>921; 8200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2166; 11026</t>
+          <t>2085; 10594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1907; 11574</t>
+          <t>1892; 11531</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4996; 17267</t>
+          <t>5071; 17262</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3760; 14966</t>
+          <t>3615; 13682</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4973; 13369</t>
+          <t>4868; 13318</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4635; 15572</t>
+          <t>3959; 15742</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13116; 31368</t>
+          <t>14049; 31352</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6329; 18740</t>
+          <t>6270; 18237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8706; 20453</t>
+          <t>8372; 20000</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4810; 15437</t>
+          <t>5303; 15694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4256; 16029</t>
+          <t>4942; 16306</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6903; 20726</t>
+          <t>7047; 21301</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13682; 28654</t>
+          <t>13397; 29729</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>957; 9494</t>
+          <t>969; 9145</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5049; 17713</t>
+          <t>5270; 17297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13237; 32659</t>
+          <t>13529; 32046</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6724; 41065</t>
+          <t>7354; 41149</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7511; 20771</t>
+          <t>7453; 22033</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12534; 29786</t>
+          <t>12991; 29791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23476; 46837</t>
+          <t>24625; 46812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17266; 65330</t>
+          <t>15723; 64309</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1617; 9353</t>
+          <t>1587; 9523</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1014; 8295</t>
+          <t>1005; 8305</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>824; 8358</t>
+          <t>823; 9087</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2231; 8097</t>
+          <t>2148; 8392</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5343; 19310</t>
+          <t>5458; 19127</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7307; 21015</t>
+          <t>7808; 22065</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1110; 8995</t>
+          <t>956; 8891</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3041; 8432</t>
+          <t>2916; 8398</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8934; 23628</t>
+          <t>8473; 23425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9725; 25172</t>
+          <t>9949; 24441</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3688; 15014</t>
+          <t>3365; 14257</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6393; 14319</t>
+          <t>6009; 14033</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7119</t>
+          <t>0; 6962</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4855; 17102</t>
+          <t>5191; 17575</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1943; 11795</t>
+          <t>1958; 12519</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2360; 9744</t>
+          <t>2442; 10416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2991; 12655</t>
+          <t>2203; 13498</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5367; 18912</t>
+          <t>6247; 19800</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4618; 18454</t>
+          <t>4955; 16843</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3280; 11664</t>
+          <t>2875; 11498</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3982; 14961</t>
+          <t>3981; 15576</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13959; 30982</t>
+          <t>13648; 30908</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9209; 23927</t>
+          <t>8879; 24449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6817; 18225</t>
+          <t>7054; 17848</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11932; 26606</t>
+          <t>12026; 27941</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16523; 36378</t>
+          <t>15749; 34981</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18116; 39683</t>
+          <t>18564; 39913</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22233; 43774</t>
+          <t>23434; 44304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13744; 31928</t>
+          <t>14076; 32759</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22763; 44811</t>
+          <t>23154; 44472</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18981; 39520</t>
+          <t>19317; 38556</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>36410; 57719</t>
+          <t>36963; 58178</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29350; 54112</t>
+          <t>28657; 52451</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44705; 74080</t>
+          <t>44564; 73214</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43366; 73361</t>
+          <t>42245; 70930</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>64056; 94472</t>
+          <t>64591; 94259</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7885; 23152</t>
+          <t>8301; 22089</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8483; 25046</t>
+          <t>8703; 24940</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8610; 23514</t>
+          <t>8876; 24256</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12624; 28103</t>
+          <t>12505; 27377</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13276; 31068</t>
+          <t>13574; 32492</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13404; 31570</t>
+          <t>14274; 31664</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17948; 40171</t>
+          <t>17205; 40195</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>31387; 50577</t>
+          <t>30579; 50176</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23949; 48102</t>
+          <t>25499; 49437</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25733; 50376</t>
+          <t>26633; 50199</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30052; 57581</t>
+          <t>31160; 56726</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>48588; 71781</t>
+          <t>48289; 72288</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>59288; 90084</t>
+          <t>59039; 90940</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>75938; 113125</t>
+          <t>75237; 113769</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71659; 109319</t>
+          <t>69880; 108106</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92863; 129600</t>
+          <t>94283; 131578</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>85481; 123824</t>
+          <t>83660; 124655</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95519; 137801</t>
+          <t>97245; 138518</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>118387; 162123</t>
+          <t>116471; 161563</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>121737; 180635</t>
+          <t>117282; 181987</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>153636; 203874</t>
+          <t>153644; 203563</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>184530; 243251</t>
+          <t>181779; 238738</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>196733; 258302</t>
+          <t>200623; 260124</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>226106; 298147</t>
+          <t>227705; 297678</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q17F_D_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 28,76</t>
+          <t>7,46; 27,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 27,62</t>
+          <t>6,59; 27,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 20,42</t>
+          <t>4,95; 21,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 16,35</t>
+          <t>4,76; 18,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 25,26</t>
+          <t>6,39; 23,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 14,04</t>
+          <t>2,19; 13,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 27,44</t>
+          <t>10,82; 26,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 25,51</t>
+          <t>10,88; 23,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 22,22</t>
+          <t>8,75; 22,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 15,65</t>
+          <t>5,19; 15,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 21,47</t>
+          <t>10,19; 20,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,38; 19,4</t>
+          <t>9,3; 18,69</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 28,7</t>
+          <t>10,85; 29,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 23,8</t>
+          <t>6,63; 23,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 20,65</t>
+          <t>7,13; 21,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,72; 36,31</t>
+          <t>13,93; 35,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 27,17</t>
+          <t>13,12; 26,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 14,26</t>
+          <t>3,72; 14,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 20,0</t>
+          <t>9,37; 20,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 25,94</t>
+          <t>11,69; 25,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,01; 24,74</t>
+          <t>13,93; 24,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 15,64</t>
+          <t>6,67; 15,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 18,04</t>
+          <t>9,4; 17,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 27,72</t>
+          <t>14,85; 27,94</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 14,56</t>
+          <t>1,64; 14,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,77</t>
+          <t>6,12; 22,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,89</t>
+          <t>1,26; 11,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 17,12</t>
+          <t>3,23; 16,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,69</t>
+          <t>2,67; 11,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 12,23</t>
+          <t>3,62; 12,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,77</t>
+          <t>3,64; 14,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 19,17</t>
+          <t>6,55; 18,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,28</t>
+          <t>2,57; 10,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,84</t>
+          <t>5,44; 13,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,84</t>
+          <t>3,33; 10,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 15,23</t>
+          <t>6,06; 14,84</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,1; 32,85</t>
+          <t>10,18; 32,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 24,03</t>
+          <t>6,32; 22,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 25,07</t>
+          <t>9,05; 24,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,53; 45,55</t>
+          <t>20,75; 44,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,17</t>
+          <t>0,87; 7,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 15,35</t>
+          <t>4,62; 16,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 24,31</t>
+          <t>10,11; 24,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 25,03</t>
+          <t>15,08; 29,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 13,8</t>
+          <t>4,67; 13,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 16,51</t>
+          <t>6,88; 15,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 21,59</t>
+          <t>11,14; 22,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 28,0</t>
+          <t>19,37; 33,4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 24,19</t>
+          <t>4,02; 21,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,28</t>
+          <t>1,98; 16,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 33,04</t>
+          <t>2,99; 33,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 46,0</t>
+          <t>12,82; 44,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 30,17</t>
+          <t>7,95; 29,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 24,51</t>
+          <t>8,29; 23,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 18,6</t>
+          <t>2,02; 18,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 31,93</t>
+          <t>10,96; 31,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 22,8</t>
+          <t>8,22; 22,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 17,33</t>
+          <t>7,09; 18,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 18,93</t>
+          <t>4,61; 20,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 31,51</t>
+          <t>14,85; 31,83</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,17</t>
+          <t>0,0; 15,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 22,62</t>
+          <t>6,59; 21,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 11,81</t>
+          <t>1,87; 11,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 19,7</t>
+          <t>5,39; 19,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 16,94</t>
+          <t>2,6; 15,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 18,49</t>
+          <t>5,72; 19,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 13,01</t>
+          <t>3,71; 13,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,92; 19,69</t>
+          <t>4,91; 19,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 12,41</t>
+          <t>3,23; 12,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 16,73</t>
+          <t>7,37; 16,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,39</t>
+          <t>3,55; 10,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 16,04</t>
+          <t>6,04; 15,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,75; 20,33</t>
+          <t>8,25; 19,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 21,33</t>
+          <t>9,73; 21,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,63; 27,15</t>
+          <t>12,47; 26,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,44; 34,87</t>
+          <t>17,74; 32,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 16,08</t>
+          <t>6,8; 15,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 20,6</t>
+          <t>10,83; 20,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,42; 22,8</t>
+          <t>11,32; 23,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,53; 32,32</t>
+          <t>21,22; 32,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,4; 15,37</t>
+          <t>8,26; 15,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,73; 19,27</t>
+          <t>11,64; 19,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,36; 22,44</t>
+          <t>13,45; 22,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,03; 30,7</t>
+          <t>21,4; 30,31</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,68; 15,11</t>
+          <t>5,43; 15,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 16,14</t>
+          <t>5,4; 15,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,22; 11,53</t>
+          <t>4,36; 11,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,1; 19,93</t>
+          <t>9,64; 21,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,99</t>
+          <t>6,38; 15,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,76</t>
+          <t>6,44; 15,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 15,41</t>
+          <t>6,45; 15,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,96; 26,19</t>
+          <t>17,16; 26,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,03; 13,62</t>
+          <t>7,03; 13,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 13,6</t>
+          <t>7,17; 13,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,04</t>
+          <t>6,44; 11,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,68; 21,98</t>
+          <t>15,1; 22,35</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,03</t>
+          <t>9,69; 15,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,25</t>
+          <t>10,15; 15,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,56; 13,24</t>
+          <t>8,61; 13,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,55; 21,7</t>
+          <t>15,78; 21,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,87</t>
+          <t>8,75; 12,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,5</t>
+          <t>8,94; 12,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,59</t>
+          <t>10,61; 14,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,77; 21,37</t>
+          <t>18,33; 22,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,77; 12,94</t>
+          <t>9,88; 13,09</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 12,88</t>
+          <t>9,92; 12,93</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,52</t>
+          <t>10,31; 13,39</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,62; 20,42</t>
+          <t>17,89; 21,58</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>19495</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3637; 13680</t>
+          <t>3546; 13055</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3933; 15724</t>
+          <t>3753; 15446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3210; 13832</t>
+          <t>3353; 14437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2363; 11219</t>
+          <t>3035; 11903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4055; 15651</t>
+          <t>3962; 14837</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2861; 12720</t>
+          <t>1988; 12375</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10936; 25711</t>
+          <t>10143; 24589</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8641; 18772</t>
+          <t>8640; 18520</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9605; 24338</t>
+          <t>9586; 24428</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8038; 23091</t>
+          <t>7661; 22414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16807; 34671</t>
+          <t>16450; 33855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13333; 27585</t>
+          <t>13309; 26747</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>34693</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9455; 24774</t>
+          <t>9367; 25559</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6065; 21081</t>
+          <t>5874; 20467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7048; 21404</t>
+          <t>7387; 21798</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11042; 27249</t>
+          <t>10816; 27564</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18236; 35937</t>
+          <t>17353; 34976</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5960; 19403</t>
+          <t>5060; 20042</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15544; 35005</t>
+          <t>16391; 35583</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10387; 22748</t>
+          <t>10622; 23275</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30617; 54068</t>
+          <t>30444; 53250</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14932; 35146</t>
+          <t>14984; 34511</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26320; 50282</t>
+          <t>26198; 49431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24634; 45113</t>
+          <t>25023; 47090</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>13459</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>936; 7939</t>
+          <t>896; 7830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5921; 19442</t>
+          <t>5228; 19234</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>921; 8200</t>
+          <t>870; 7704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2085; 10594</t>
+          <t>2021; 10532</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1892; 11531</t>
+          <t>2635; 11544</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5071; 17262</t>
+          <t>5105; 17186</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3615; 13682</t>
+          <t>3618; 14168</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4868; 13318</t>
+          <t>4707; 13349</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3959; 15742</t>
+          <t>3933; 15724</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14049; 31352</t>
+          <t>12329; 30219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6270; 18237</t>
+          <t>5602; 18264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8372; 20000</t>
+          <t>8148; 19965</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21147</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41458</t>
+          <t>47370</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5303; 15694</t>
+          <t>4863; 15499</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4942; 16306</t>
+          <t>4291; 15410</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7047; 21301</t>
+          <t>7685; 20811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13397; 29729</t>
+          <t>16149; 34924</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>969; 9145</t>
+          <t>968; 8494</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5270; 17297</t>
+          <t>5203; 18456</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13529; 32046</t>
+          <t>13322; 31877</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7354; 41149</t>
+          <t>16085; 31282</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7453; 22033</t>
+          <t>7455; 21081</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12991; 29791</t>
+          <t>12421; 28730</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24625; 46812</t>
+          <t>24158; 48463</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15723; 64309</t>
+          <t>35742; 61617</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10652</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1587; 9523</t>
+          <t>1582; 8625</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1005; 8305</t>
+          <t>1009; 8410</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>823; 9087</t>
+          <t>822; 9182</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2148; 8392</t>
+          <t>2498; 8766</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5458; 19127</t>
+          <t>5041; 18593</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7808; 22065</t>
+          <t>7463; 21236</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>956; 8891</t>
+          <t>965; 8792</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2916; 8398</t>
+          <t>3144; 9046</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8473; 23425</t>
+          <t>8444; 23572</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9949; 24441</t>
+          <t>9995; 25399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3365; 14257</t>
+          <t>3474; 15134</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6009; 14033</t>
+          <t>7153; 15329</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11332</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6962</t>
+          <t>0; 6967</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5191; 17575</t>
+          <t>5118; 17026</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1958; 12519</t>
+          <t>1979; 12092</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2442; 10416</t>
+          <t>2757; 9784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2203; 13498</t>
+          <t>2072; 12145</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6247; 19800</t>
+          <t>6124; 20600</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4955; 16843</t>
+          <t>4797; 17525</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2875; 11498</t>
+          <t>2928; 11811</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3981; 15576</t>
+          <t>4057; 15099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13648; 30908</t>
+          <t>13615; 30323</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8879; 24449</t>
+          <t>8367; 24903</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7054; 17848</t>
+          <t>6691; 17387</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>34926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>46655</t>
+          <t>58832</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78550</t>
+          <t>93758</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12026; 27941</t>
+          <t>11342; 26261</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15749; 34981</t>
+          <t>15954; 35696</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18564; 39913</t>
+          <t>18329; 39265</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23434; 44304</t>
+          <t>25728; 46739</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14076; 32759</t>
+          <t>13853; 32442</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23154; 44472</t>
+          <t>23391; 44478</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19317; 38556</t>
+          <t>19144; 39729</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>36963; 58178</t>
+          <t>46834; 71136</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28657; 52451</t>
+          <t>28183; 53735</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44564; 73214</t>
+          <t>44223; 73342</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42245; 70930</t>
+          <t>42514; 69994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>64591; 94259</t>
+          <t>78272; 110851</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>40318</t>
+          <t>46541</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59453</t>
+          <t>68488</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8301; 22089</t>
+          <t>7934; 22189</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8703; 24940</t>
+          <t>8344; 24554</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8876; 24256</t>
+          <t>9184; 25090</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12505; 27377</t>
+          <t>14872; 32471</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13574; 32492</t>
+          <t>13832; 33298</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14274; 31664</t>
+          <t>13813; 33036</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17205; 40195</t>
+          <t>16818; 39381</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>30579; 50176</t>
+          <t>37003; 57096</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25499; 49437</t>
+          <t>25521; 48666</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26633; 50199</t>
+          <t>26479; 51072</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31160; 56726</t>
+          <t>30369; 56167</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>48289; 72288</t>
+          <t>55847; 82651</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>120965</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>157091</t>
+          <t>178282</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>267744</t>
+          <t>299248</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>59039; 90940</t>
+          <t>58656; 91638</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>75237; 113769</t>
+          <t>75691; 113651</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>69880; 108106</t>
+          <t>70285; 107819</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>94283; 131578</t>
+          <t>102826; 142922</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>83660; 124655</t>
+          <t>84711; 124464</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97245; 138518</t>
+          <t>99034; 139149</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>116471; 161563</t>
+          <t>117428; 164343</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>117282; 181987</t>
+          <t>160135; 200627</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>153644; 203563</t>
+          <t>155508; 205889</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>181779; 238738</t>
+          <t>183941; 239724</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>200623; 260124</t>
+          <t>198395; 257585</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>227705; 297678</t>
+          <t>272816; 329167</t>
         </is>
       </c>
     </row>
